--- a/doctor_schedule_sample.xlsx
+++ b/doctor_schedule_sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\Ky_9\FSOFT\CARE_SLOT\BE\care-slot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8BC77B-B458-4BC9-8A64-165BE9B725A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2F5F28-CB86-4C3E-A930-5EE510009902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>Doctor ID</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Room Name</t>
-  </si>
-  <si>
-    <t>2026-09-10</t>
   </si>
   <si>
     <t>08:00</t>
@@ -100,8 +97,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -433,85 +431,85 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1">
+        <v>46270</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="B3" s="1">
+        <v>46270</v>
       </c>
       <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
+      <c r="B4" s="1">
+        <v>46270</v>
       </c>
       <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
+      <c r="B5" s="1">
+        <v>46270</v>
       </c>
       <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
+      <c r="B6" s="1">
+        <v>46270</v>
       </c>
       <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
         <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
